--- a/data/trans_dic/DCD_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/DCD_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 15,3</t>
+          <t>8,54; 15,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,04; 22,06</t>
+          <t>15,08; 22,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,24; 17,27</t>
+          <t>12,43; 17,38</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,53; 16,53</t>
+          <t>9,39; 15,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,06; 31,85</t>
+          <t>25,35; 32,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,81; 22,95</t>
+          <t>17,99; 22,93</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 22,43</t>
+          <t>14,36; 22,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,31; 34,19</t>
+          <t>26,37; 33,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,44; 27,21</t>
+          <t>21,6; 27,21</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,67; 21,5</t>
+          <t>12,56; 21,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,35; 28,93</t>
+          <t>14,1; 29,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,38; 23,81</t>
+          <t>14,66; 24,07</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,02; 15,46</t>
+          <t>7,81; 15,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,94; 21,99</t>
+          <t>8,35; 22,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 17,35</t>
+          <t>9,87; 17,59</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,91; 25,36</t>
+          <t>17,22; 24,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,03; 40,45</t>
+          <t>31,26; 40,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,85; 31,37</t>
+          <t>25,26; 31,25</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,55; 19,61</t>
+          <t>13,5; 19,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,71; 37,76</t>
+          <t>13,37; 37,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,8; 27,54</t>
+          <t>15,59; 27,62</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,81</t>
+          <t>3,67; 11,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,66; 26,02</t>
+          <t>20,47; 25,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,21; 17,87</t>
+          <t>9,34; 17,96</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,42; 14,94</t>
+          <t>10,55; 15,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,8; 27,7</t>
+          <t>20,58; 27,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,11; 21,21</t>
+          <t>16,92; 21,14</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25293; 47636</t>
+          <t>26585; 47454</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43563; 63894</t>
+          <t>43691; 63906</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73571; 103780</t>
+          <t>74711; 104456</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49415; 85673</t>
+          <t>48670; 81163</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>129061; 164022</t>
+          <t>130543; 165480</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>184060; 237190</t>
+          <t>185908; 236990</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45934; 70894</t>
+          <t>45370; 70275</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91858; 119354</t>
+          <t>92077; 118246</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>142628; 180972</t>
+          <t>143681; 181003</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158582</t>
+          <t>158581</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39616; 67200</t>
+          <t>39250; 67491</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63486; 137628</t>
+          <t>67062; 139108</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121204; 187675</t>
+          <t>115579; 189743</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14342; 27633</t>
+          <t>13963; 26977</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20541; 56911</t>
+          <t>21619; 57366</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40974; 75914</t>
+          <t>43173; 76950</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>45604; 68378</t>
+          <t>46434; 67330</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79768; 103980</t>
+          <t>80350; 104020</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>130895; 165214</t>
+          <t>133065; 164589</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>340894</t>
+          <t>340893</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>84604; 122442</t>
+          <t>84299; 123283</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>124896; 320676</t>
+          <t>113506; 321055</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>203329; 405816</t>
+          <t>229740; 406939</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>34412; 109724</t>
+          <t>34103; 109925</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>148288; 186763</t>
+          <t>146906; 184382</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>151672; 294267</t>
+          <t>153753; 295736</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>360611; 516813</t>
+          <t>364903; 519297</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>772295; 1028292</t>
+          <t>764091; 1028185</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1227473; 1521176</t>
+          <t>1213709; 1516243</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DCD_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/DCD_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,24</t>
+          <t>8,28; 14,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,08; 22,06</t>
+          <t>15,5; 22,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,43; 17,38</t>
+          <t>12,96; 17,55</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 15,66</t>
+          <t>9,37; 16,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,35; 32,13</t>
+          <t>24,83; 31,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,99; 22,93</t>
+          <t>17,77; 23,04</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,36; 22,24</t>
+          <t>13,98; 21,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,37; 33,87</t>
+          <t>25,91; 33,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 27,21</t>
+          <t>21,41; 26,69</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,56; 21,59</t>
+          <t>11,21; 19,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 29,24</t>
+          <t>24,57; 32,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 24,07</t>
+          <t>18,87; 24,78</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,81; 15,09</t>
+          <t>7,21; 14,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 22,17</t>
+          <t>16,24; 23,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,87; 17,59</t>
+          <t>12,92; 17,95</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,22; 24,97</t>
+          <t>17,07; 24,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,26; 40,47</t>
+          <t>30,84; 40,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,26; 31,25</t>
+          <t>24,63; 30,91</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,5; 19,75</t>
+          <t>13,71; 19,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,37; 37,8</t>
+          <t>34,15; 40,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,59; 27,62</t>
+          <t>25,04; 29,8</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,67; 11,84</t>
+          <t>8,98; 12,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,47; 25,69</t>
+          <t>20,31; 25,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,34; 17,96</t>
+          <t>15,31; 18,55</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,55; 15,01</t>
+          <t>12,96; 15,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,58; 27,7</t>
+          <t>26,92; 29,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,92; 21,14</t>
+          <t>20,32; 22,12</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35365</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53312</t>
+          <t>59418</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88677</t>
+          <t>95867</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26585; 47454</t>
+          <t>26402; 47692</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43691; 63906</t>
+          <t>48994; 70584</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74711; 104456</t>
+          <t>82253; 111446</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>63358</t>
+          <t>65172</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>147092</t>
+          <t>153144</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>210450</t>
+          <t>218316</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48670; 81163</t>
+          <t>49705; 85042</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>130543; 165480</t>
+          <t>135691; 173486</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>185908; 236990</t>
+          <t>191459; 248174</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56592</t>
+          <t>56435</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>103862</t>
+          <t>105676</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160454</t>
+          <t>162111</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45370; 70275</t>
+          <t>44184; 68914</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92077; 118246</t>
+          <t>92348; 119303</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143681; 181003</t>
+          <t>143944; 179434</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>55606</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>107156</t>
+          <t>118408</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158581</t>
+          <t>174014</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39250; 67491</t>
+          <t>41837; 72180</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67062; 139108</t>
+          <t>103687; 137913</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115579; 189743</t>
+          <t>150001; 197031</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>21180</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43327</t>
+          <t>45017</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63347</t>
+          <t>66197</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13963; 26977</t>
+          <t>14820; 28981</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21619; 57366</t>
+          <t>37184; 53751</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43173; 76950</t>
+          <t>56160; 77987</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>56255</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>91452</t>
+          <t>93328</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>147706</t>
+          <t>148932</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46434; 67330</t>
+          <t>46203; 67187</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>80350; 104020</t>
+          <t>81347; 105935</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133065; 164589</t>
+          <t>131653; 165225</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>103280</t>
+          <t>119774</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>237613</t>
+          <t>288074</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>340893</t>
+          <t>407849</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>84299; 123283</t>
+          <t>98688; 141085</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>113506; 321055</t>
+          <t>263638; 312982</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>229740; 406939</t>
+          <t>373490; 444489</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>76284</t>
+          <t>86117</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>165731</t>
+          <t>187172</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>242016</t>
+          <t>273290</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>34103; 109925</t>
+          <t>71687; 102816</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>146906; 184382</t>
+          <t>168884; 208723</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>153753; 295736</t>
+          <t>249536; 302229</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>462580</t>
+          <t>496338</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>949546</t>
+          <t>1050237</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1412125</t>
+          <t>1546575</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>364903; 519297</t>
+          <t>457883; 543216</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>764091; 1028185</t>
+          <t>1006147; 1101531</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1213709; 1516243</t>
+          <t>1477371; 1607726</t>
         </is>
       </c>
     </row>
